--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.77.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.77.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.77.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.77.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="51" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.77.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.77.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0077.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0077.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -597,26 +597,34 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: vice of subpo Ã¦ e-</t>
+          <t>L115: stray/suspicious non-ASCII glyph(s): U+5E7F CJK UNIFIED IDEOGRAPH-5E7F | isolated marker/symbol line :: 广</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Masterâ€™s refu-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]70</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]70</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L46: isolated marker/symbol line :: 70</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]70</t>
+        </is>
+      </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L52: punctuation artifact: repeated periods :: down the cause. Â°..</t>
+          <t>L52: punctuation artifact: repeated periods :: down the cause. °..</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -641,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -650,16 +658,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: 1. Within fourteen dnys after service of a subpoe Ã¦ ena to</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Defendant, to 1â€”</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -701,16 +701,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: eight days after the service of the subp Ã¦ ena to an-</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the Order :â€”</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -738,12 +730,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -752,15 +744,15 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the Order :â€” :â€”</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
-      <c r="N5" s="1" t="inlineStr"/>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>L115: stray/suspicious non-ASCII glyph(s): U+5E7F CJK UNIFIED IDEOGRAPH-5E7F | isolated marker/symbol line :: 广</t>
+        </is>
+      </c>
       <c r="O5" s="1" t="inlineStr"/>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
@@ -795,11 +787,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œIf the Pl:</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -941,12 +929,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -985,7 +973,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1019,12 +1007,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
